--- a/data/monthly/【2025年7月】月次数値.xlsx
+++ b/data/monthly/【2025年7月】月次数値.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="85">
   <si>
     <t>レポート開始日</t>
   </si>
@@ -195,6 +195,87 @@
   <si>
     <t>Instagram投稿: 【銀座トレーニングラボ】
 “脚が変わる”は、立ち方から始まる。...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【Dining Bar Lien】...</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【Meibuキッズ空手教室】
+＼ドキドキ💓はじめてのスポーツ体験！／...</t>
+  </si>
+  <si>
+    <t>2026-01-02</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【Meibuキッズ空手教室】
+＼2〜3歳のお子さまも大歓迎👶✨／...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 📍町寿司いちもんめ｜福井市大手...</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌸【女性クリニック ラポール】🌸
+すべての世代の女性に、安心と寄り添いを。...</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【髙橋歯科】
+“噛み合わせ”から整える、お口とカラダのトータルケア🪥...</t>
+  </si>
+  <si>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 📍Wild Crepes - ワイルドクレープス
+安い！旨い！多い！🎉...</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍸【bar moon walk 三条木屋町店】🌙...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍶【駕町 とくさ】熊本・花畑町駅 徒歩5分...</t>
+  </si>
+  <si>
+    <t>炭焼　猿一</t>
+  </si>
+  <si>
+    <t>2026-01-15</t>
+  </si>
+  <si>
+    <t>島田屋　東苗穂店</t>
+  </si>
+  <si>
+    <t>居ZAKKU　CHENOWA</t>
+  </si>
+  <si>
+    <t>三千段の民宿　幸登里</t>
+  </si>
+  <si>
+    <t>てんぐ屋</t>
+  </si>
+  <si>
+    <t>炭火焼肉友丸</t>
+  </si>
+  <si>
+    <t>旬彩屋　笑味</t>
+  </si>
+  <si>
+    <t>有限会社　大嶋_うまか喰い処 祇園 大しま</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【海鮮と肉料理 ほっかい酒房】🍣🍢✨
+すすきの駅から徒歩3分🚶‍♂️...</t>
   </si>
 </sst>
 </file>
@@ -545,7 +626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y17"/>
+  <dimension ref="A1:Y35"/>
   <sheetFormatPr defaultColWidth="20" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.3">
@@ -1523,7 +1604,7 @@
         <v>28.095237999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -1597,7 +1678,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -1669,6 +1750,1230 @@
       </c>
       <c r="Y17">
         <v>63</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" t="s">
+        <v>29</v>
+      </c>
+      <c r="F18">
+        <v>199</v>
+      </c>
+      <c r="G18" t="s">
+        <v>30</v>
+      </c>
+      <c r="H18">
+        <v>4493</v>
+      </c>
+      <c r="I18">
+        <v>1.900067</v>
+      </c>
+      <c r="J18">
+        <v>24.16582915</v>
+      </c>
+      <c r="K18">
+        <v>160</v>
+      </c>
+      <c r="L18" t="s">
+        <v>31</v>
+      </c>
+      <c r="M18">
+        <v>4809</v>
+      </c>
+      <c r="N18" t="s">
+        <v>61</v>
+      </c>
+      <c r="O18">
+        <v>8537</v>
+      </c>
+      <c r="P18">
+        <v>563.31263899999999</v>
+      </c>
+      <c r="Q18">
+        <v>199</v>
+      </c>
+      <c r="S18">
+        <v>24.165828999999999</v>
+      </c>
+      <c r="T18">
+        <v>2.3310300000000002</v>
+      </c>
+      <c r="U18">
+        <v>310</v>
+      </c>
+      <c r="V18">
+        <v>3.6312519999999999</v>
+      </c>
+      <c r="W18">
+        <v>15.512903</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" t="s">
+        <v>62</v>
+      </c>
+      <c r="D19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E19" t="s">
+        <v>29</v>
+      </c>
+      <c r="F19">
+        <v>85</v>
+      </c>
+      <c r="G19" t="s">
+        <v>30</v>
+      </c>
+      <c r="H19">
+        <v>3462</v>
+      </c>
+      <c r="I19">
+        <v>1.3495090000000001</v>
+      </c>
+      <c r="J19">
+        <v>51.247058819999999</v>
+      </c>
+      <c r="K19">
+        <v>160</v>
+      </c>
+      <c r="L19" t="s">
+        <v>31</v>
+      </c>
+      <c r="M19">
+        <v>4356</v>
+      </c>
+      <c r="N19" t="s">
+        <v>63</v>
+      </c>
+      <c r="O19">
+        <v>4672</v>
+      </c>
+      <c r="P19">
+        <v>932.36301400000002</v>
+      </c>
+      <c r="Q19">
+        <v>85</v>
+      </c>
+      <c r="S19">
+        <v>51.247059</v>
+      </c>
+      <c r="T19">
+        <v>1.8193490000000001</v>
+      </c>
+      <c r="U19">
+        <v>102</v>
+      </c>
+      <c r="V19">
+        <v>2.1832189999999998</v>
+      </c>
+      <c r="W19">
+        <v>42.705882000000003</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" t="s">
+        <v>29</v>
+      </c>
+      <c r="F20">
+        <v>217</v>
+      </c>
+      <c r="G20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H20">
+        <v>4254</v>
+      </c>
+      <c r="I20">
+        <v>1.396333</v>
+      </c>
+      <c r="J20">
+        <v>19.986175119999999</v>
+      </c>
+      <c r="K20">
+        <v>160</v>
+      </c>
+      <c r="L20" t="s">
+        <v>31</v>
+      </c>
+      <c r="M20">
+        <v>4337</v>
+      </c>
+      <c r="N20" t="s">
+        <v>63</v>
+      </c>
+      <c r="O20">
+        <v>5940</v>
+      </c>
+      <c r="P20">
+        <v>730.13468</v>
+      </c>
+      <c r="Q20">
+        <v>217</v>
+      </c>
+      <c r="S20">
+        <v>19.986174999999999</v>
+      </c>
+      <c r="T20">
+        <v>3.6531989999999999</v>
+      </c>
+      <c r="U20">
+        <v>322</v>
+      </c>
+      <c r="V20">
+        <v>5.4208749999999997</v>
+      </c>
+      <c r="W20">
+        <v>13.468944</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" t="s">
+        <v>65</v>
+      </c>
+      <c r="D21" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" t="s">
+        <v>29</v>
+      </c>
+      <c r="F21">
+        <v>183</v>
+      </c>
+      <c r="G21" t="s">
+        <v>30</v>
+      </c>
+      <c r="H21">
+        <v>2917</v>
+      </c>
+      <c r="I21">
+        <v>1.53891</v>
+      </c>
+      <c r="J21">
+        <v>21.24590164</v>
+      </c>
+      <c r="K21">
+        <v>160</v>
+      </c>
+      <c r="L21" t="s">
+        <v>31</v>
+      </c>
+      <c r="M21">
+        <v>3888</v>
+      </c>
+      <c r="N21" t="s">
+        <v>66</v>
+      </c>
+      <c r="O21">
+        <v>4489</v>
+      </c>
+      <c r="P21">
+        <v>866.11717499999997</v>
+      </c>
+      <c r="Q21">
+        <v>183</v>
+      </c>
+      <c r="S21">
+        <v>21.245902000000001</v>
+      </c>
+      <c r="T21">
+        <v>4.076632</v>
+      </c>
+      <c r="U21">
+        <v>207</v>
+      </c>
+      <c r="V21">
+        <v>4.6112719999999996</v>
+      </c>
+      <c r="W21">
+        <v>18.782609000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" t="s">
+        <v>67</v>
+      </c>
+      <c r="D22" t="s">
+        <v>44</v>
+      </c>
+      <c r="E22" t="s">
+        <v>29</v>
+      </c>
+      <c r="F22">
+        <v>121</v>
+      </c>
+      <c r="G22" t="s">
+        <v>30</v>
+      </c>
+      <c r="H22">
+        <v>2518</v>
+      </c>
+      <c r="I22">
+        <v>1.657268</v>
+      </c>
+      <c r="J22">
+        <v>29.454545450000001</v>
+      </c>
+      <c r="K22">
+        <v>160</v>
+      </c>
+      <c r="L22" t="s">
+        <v>31</v>
+      </c>
+      <c r="M22">
+        <v>3564</v>
+      </c>
+      <c r="N22" t="s">
+        <v>68</v>
+      </c>
+      <c r="O22">
+        <v>4173</v>
+      </c>
+      <c r="P22">
+        <v>854.061826</v>
+      </c>
+      <c r="Q22">
+        <v>121</v>
+      </c>
+      <c r="S22">
+        <v>29.454545</v>
+      </c>
+      <c r="T22">
+        <v>2.8995929999999999</v>
+      </c>
+      <c r="U22">
+        <v>146</v>
+      </c>
+      <c r="V22">
+        <v>3.4986820000000001</v>
+      </c>
+      <c r="W22">
+        <v>24.410958999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" t="s">
+        <v>69</v>
+      </c>
+      <c r="D23" t="s">
+        <v>28</v>
+      </c>
+      <c r="E23" t="s">
+        <v>29</v>
+      </c>
+      <c r="F23">
+        <v>102</v>
+      </c>
+      <c r="G23" t="s">
+        <v>30</v>
+      </c>
+      <c r="H23">
+        <v>2351</v>
+      </c>
+      <c r="I23">
+        <v>1.455125</v>
+      </c>
+      <c r="J23">
+        <v>33.656862750000002</v>
+      </c>
+      <c r="K23">
+        <v>160</v>
+      </c>
+      <c r="L23" t="s">
+        <v>31</v>
+      </c>
+      <c r="M23">
+        <v>3433</v>
+      </c>
+      <c r="N23" t="s">
+        <v>70</v>
+      </c>
+      <c r="O23">
+        <v>3421</v>
+      </c>
+      <c r="P23">
+        <v>1003.507746</v>
+      </c>
+      <c r="Q23">
+        <v>102</v>
+      </c>
+      <c r="S23">
+        <v>33.656863000000001</v>
+      </c>
+      <c r="T23">
+        <v>2.9815839999999998</v>
+      </c>
+      <c r="U23">
+        <v>122</v>
+      </c>
+      <c r="V23">
+        <v>3.5662090000000002</v>
+      </c>
+      <c r="W23">
+        <v>28.139344000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" t="s">
+        <v>71</v>
+      </c>
+      <c r="D24" t="s">
+        <v>44</v>
+      </c>
+      <c r="E24" t="s">
+        <v>29</v>
+      </c>
+      <c r="F24">
+        <v>214</v>
+      </c>
+      <c r="G24" t="s">
+        <v>30</v>
+      </c>
+      <c r="H24">
+        <v>3389</v>
+      </c>
+      <c r="I24">
+        <v>1.6509290000000001</v>
+      </c>
+      <c r="J24">
+        <v>13.01869159</v>
+      </c>
+      <c r="K24">
+        <v>160</v>
+      </c>
+      <c r="L24" t="s">
+        <v>31</v>
+      </c>
+      <c r="M24">
+        <v>2786</v>
+      </c>
+      <c r="N24" t="s">
+        <v>72</v>
+      </c>
+      <c r="O24">
+        <v>5595</v>
+      </c>
+      <c r="P24">
+        <v>497.944593</v>
+      </c>
+      <c r="Q24">
+        <v>214</v>
+      </c>
+      <c r="S24">
+        <v>13.018692</v>
+      </c>
+      <c r="T24">
+        <v>3.8248440000000001</v>
+      </c>
+      <c r="U24">
+        <v>288</v>
+      </c>
+      <c r="V24">
+        <v>5.1474529999999996</v>
+      </c>
+      <c r="W24">
+        <v>9.6736109999999993</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" t="s">
+        <v>73</v>
+      </c>
+      <c r="D25" t="s">
+        <v>44</v>
+      </c>
+      <c r="E25" t="s">
+        <v>29</v>
+      </c>
+      <c r="F25">
+        <v>58</v>
+      </c>
+      <c r="G25" t="s">
+        <v>30</v>
+      </c>
+      <c r="H25">
+        <v>2168</v>
+      </c>
+      <c r="I25">
+        <v>1.494926</v>
+      </c>
+      <c r="J25">
+        <v>48.448275860000003</v>
+      </c>
+      <c r="K25">
+        <v>160</v>
+      </c>
+      <c r="L25" t="s">
+        <v>31</v>
+      </c>
+      <c r="M25">
+        <v>2810</v>
+      </c>
+      <c r="N25" t="s">
+        <v>72</v>
+      </c>
+      <c r="O25">
+        <v>3241</v>
+      </c>
+      <c r="P25">
+        <v>867.01635299999998</v>
+      </c>
+      <c r="Q25">
+        <v>58</v>
+      </c>
+      <c r="S25">
+        <v>48.448276</v>
+      </c>
+      <c r="T25">
+        <v>1.789571</v>
+      </c>
+      <c r="U25">
+        <v>87</v>
+      </c>
+      <c r="V25">
+        <v>2.6843569999999999</v>
+      </c>
+      <c r="W25">
+        <v>32.298850999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" t="s">
+        <v>74</v>
+      </c>
+      <c r="D26" t="s">
+        <v>44</v>
+      </c>
+      <c r="E26" t="s">
+        <v>29</v>
+      </c>
+      <c r="F26">
+        <v>241</v>
+      </c>
+      <c r="G26" t="s">
+        <v>30</v>
+      </c>
+      <c r="H26">
+        <v>2416</v>
+      </c>
+      <c r="I26">
+        <v>1.7740069999999999</v>
+      </c>
+      <c r="J26">
+        <v>11.568464730000001</v>
+      </c>
+      <c r="K26">
+        <v>160</v>
+      </c>
+      <c r="L26" t="s">
+        <v>31</v>
+      </c>
+      <c r="M26">
+        <v>2788</v>
+      </c>
+      <c r="N26" t="s">
+        <v>72</v>
+      </c>
+      <c r="O26">
+        <v>4286</v>
+      </c>
+      <c r="P26">
+        <v>650.48996699999998</v>
+      </c>
+      <c r="Q26">
+        <v>241</v>
+      </c>
+      <c r="S26">
+        <v>11.568465</v>
+      </c>
+      <c r="T26">
+        <v>5.6229579999999997</v>
+      </c>
+      <c r="U26">
+        <v>286</v>
+      </c>
+      <c r="V26">
+        <v>6.6728880000000004</v>
+      </c>
+      <c r="W26">
+        <v>9.7482520000000008</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>26</v>
+      </c>
+      <c r="C27" t="s">
+        <v>75</v>
+      </c>
+      <c r="D27" t="s">
+        <v>44</v>
+      </c>
+      <c r="E27" t="s">
+        <v>29</v>
+      </c>
+      <c r="F27">
+        <v>212</v>
+      </c>
+      <c r="G27" t="s">
+        <v>30</v>
+      </c>
+      <c r="H27">
+        <v>3624</v>
+      </c>
+      <c r="I27">
+        <v>1.5091060000000001</v>
+      </c>
+      <c r="J27">
+        <v>13.04245283</v>
+      </c>
+      <c r="K27" t="s">
+        <v>37</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>2765</v>
+      </c>
+      <c r="N27" t="s">
+        <v>76</v>
+      </c>
+      <c r="O27">
+        <v>5469</v>
+      </c>
+      <c r="P27">
+        <v>505.576888</v>
+      </c>
+      <c r="Q27">
+        <v>212</v>
+      </c>
+      <c r="S27">
+        <v>13.042453</v>
+      </c>
+      <c r="T27">
+        <v>3.8763939999999999</v>
+      </c>
+      <c r="U27">
+        <v>247</v>
+      </c>
+      <c r="V27">
+        <v>4.5163650000000004</v>
+      </c>
+      <c r="W27">
+        <v>11.194331999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" t="s">
+        <v>26</v>
+      </c>
+      <c r="C28" t="s">
+        <v>77</v>
+      </c>
+      <c r="D28" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28" t="s">
+        <v>29</v>
+      </c>
+      <c r="F28">
+        <v>221</v>
+      </c>
+      <c r="G28" t="s">
+        <v>30</v>
+      </c>
+      <c r="H28">
+        <v>4817</v>
+      </c>
+      <c r="I28">
+        <v>1.3230230000000001</v>
+      </c>
+      <c r="J28">
+        <v>12.452488689999999</v>
+      </c>
+      <c r="K28" t="s">
+        <v>37</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>2752</v>
+      </c>
+      <c r="N28" t="s">
+        <v>76</v>
+      </c>
+      <c r="O28">
+        <v>6373</v>
+      </c>
+      <c r="P28">
+        <v>431.82174800000001</v>
+      </c>
+      <c r="Q28">
+        <v>221</v>
+      </c>
+      <c r="S28">
+        <v>12.452489</v>
+      </c>
+      <c r="T28">
+        <v>3.4677549999999999</v>
+      </c>
+      <c r="U28">
+        <v>241</v>
+      </c>
+      <c r="V28">
+        <v>3.7815789999999998</v>
+      </c>
+      <c r="W28">
+        <v>11.419086999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29" t="s">
+        <v>78</v>
+      </c>
+      <c r="D29" t="s">
+        <v>44</v>
+      </c>
+      <c r="E29" t="s">
+        <v>29</v>
+      </c>
+      <c r="F29">
+        <v>106</v>
+      </c>
+      <c r="G29" t="s">
+        <v>30</v>
+      </c>
+      <c r="H29">
+        <v>2819</v>
+      </c>
+      <c r="I29">
+        <v>1.465768</v>
+      </c>
+      <c r="J29">
+        <v>27.150943399999999</v>
+      </c>
+      <c r="K29" t="s">
+        <v>37</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>2878</v>
+      </c>
+      <c r="N29" t="s">
+        <v>38</v>
+      </c>
+      <c r="O29">
+        <v>4132</v>
+      </c>
+      <c r="P29">
+        <v>696.51500499999997</v>
+      </c>
+      <c r="Q29">
+        <v>106</v>
+      </c>
+      <c r="S29">
+        <v>27.150943000000002</v>
+      </c>
+      <c r="T29">
+        <v>2.5653440000000001</v>
+      </c>
+      <c r="U29">
+        <v>157</v>
+      </c>
+      <c r="V29">
+        <v>3.7996129999999999</v>
+      </c>
+      <c r="W29">
+        <v>18.331209999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>25</v>
+      </c>
+      <c r="B30" t="s">
+        <v>26</v>
+      </c>
+      <c r="C30" t="s">
+        <v>79</v>
+      </c>
+      <c r="D30" t="s">
+        <v>44</v>
+      </c>
+      <c r="E30" t="s">
+        <v>29</v>
+      </c>
+      <c r="F30">
+        <v>88</v>
+      </c>
+      <c r="G30" t="s">
+        <v>30</v>
+      </c>
+      <c r="H30">
+        <v>2188</v>
+      </c>
+      <c r="I30">
+        <v>1.5987199999999999</v>
+      </c>
+      <c r="J30">
+        <v>33.25</v>
+      </c>
+      <c r="K30" t="s">
+        <v>37</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>2926</v>
+      </c>
+      <c r="N30" t="s">
+        <v>76</v>
+      </c>
+      <c r="O30">
+        <v>3498</v>
+      </c>
+      <c r="P30">
+        <v>836.47798699999998</v>
+      </c>
+      <c r="Q30">
+        <v>88</v>
+      </c>
+      <c r="S30">
+        <v>33.25</v>
+      </c>
+      <c r="T30">
+        <v>2.5157229999999999</v>
+      </c>
+      <c r="U30">
+        <v>102</v>
+      </c>
+      <c r="V30">
+        <v>2.9159519999999999</v>
+      </c>
+      <c r="W30">
+        <v>28.686274999999998</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" t="s">
+        <v>26</v>
+      </c>
+      <c r="C31" t="s">
+        <v>80</v>
+      </c>
+      <c r="D31" t="s">
+        <v>44</v>
+      </c>
+      <c r="E31" t="s">
+        <v>29</v>
+      </c>
+      <c r="F31">
+        <v>297</v>
+      </c>
+      <c r="G31" t="s">
+        <v>30</v>
+      </c>
+      <c r="H31">
+        <v>3568</v>
+      </c>
+      <c r="I31">
+        <v>1.4873879999999999</v>
+      </c>
+      <c r="J31">
+        <v>9.2828282800000004</v>
+      </c>
+      <c r="K31" t="s">
+        <v>37</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>2757</v>
+      </c>
+      <c r="N31" t="s">
+        <v>38</v>
+      </c>
+      <c r="O31">
+        <v>5307</v>
+      </c>
+      <c r="P31">
+        <v>519.50254399999994</v>
+      </c>
+      <c r="Q31">
+        <v>297</v>
+      </c>
+      <c r="S31">
+        <v>9.2828280000000003</v>
+      </c>
+      <c r="T31">
+        <v>5.5963820000000002</v>
+      </c>
+      <c r="U31">
+        <v>340</v>
+      </c>
+      <c r="V31">
+        <v>6.4066330000000002</v>
+      </c>
+      <c r="W31">
+        <v>8.1088240000000003</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>25</v>
+      </c>
+      <c r="B32" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" t="s">
+        <v>81</v>
+      </c>
+      <c r="D32" t="s">
+        <v>44</v>
+      </c>
+      <c r="E32" t="s">
+        <v>29</v>
+      </c>
+      <c r="F32">
+        <v>166</v>
+      </c>
+      <c r="G32" t="s">
+        <v>30</v>
+      </c>
+      <c r="H32">
+        <v>3093</v>
+      </c>
+      <c r="I32">
+        <v>1.6075010000000001</v>
+      </c>
+      <c r="J32">
+        <v>17.078313250000001</v>
+      </c>
+      <c r="K32" t="s">
+        <v>37</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>2835</v>
+      </c>
+      <c r="N32" t="s">
+        <v>38</v>
+      </c>
+      <c r="O32">
+        <v>4972</v>
+      </c>
+      <c r="P32">
+        <v>570.19308100000001</v>
+      </c>
+      <c r="Q32">
+        <v>166</v>
+      </c>
+      <c r="S32">
+        <v>17.078313000000001</v>
+      </c>
+      <c r="T32">
+        <v>3.3386969999999998</v>
+      </c>
+      <c r="U32">
+        <v>207</v>
+      </c>
+      <c r="V32">
+        <v>4.1633149999999999</v>
+      </c>
+      <c r="W32">
+        <v>13.695652000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>25</v>
+      </c>
+      <c r="B33" t="s">
+        <v>26</v>
+      </c>
+      <c r="C33" t="s">
+        <v>82</v>
+      </c>
+      <c r="D33" t="s">
+        <v>44</v>
+      </c>
+      <c r="E33" t="s">
+        <v>29</v>
+      </c>
+      <c r="F33">
+        <v>138</v>
+      </c>
+      <c r="G33" t="s">
+        <v>30</v>
+      </c>
+      <c r="H33">
+        <v>3384</v>
+      </c>
+      <c r="I33">
+        <v>1.638002</v>
+      </c>
+      <c r="J33">
+        <v>19.811594199999998</v>
+      </c>
+      <c r="K33" t="s">
+        <v>37</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>2734</v>
+      </c>
+      <c r="N33" t="s">
+        <v>38</v>
+      </c>
+      <c r="O33">
+        <v>5543</v>
+      </c>
+      <c r="P33">
+        <v>493.23471000000001</v>
+      </c>
+      <c r="Q33">
+        <v>138</v>
+      </c>
+      <c r="S33">
+        <v>19.811593999999999</v>
+      </c>
+      <c r="T33">
+        <v>2.489627</v>
+      </c>
+      <c r="U33">
+        <v>172</v>
+      </c>
+      <c r="V33">
+        <v>3.1030129999999998</v>
+      </c>
+      <c r="W33">
+        <v>15.895349</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>25</v>
+      </c>
+      <c r="B34" t="s">
+        <v>26</v>
+      </c>
+      <c r="C34" t="s">
+        <v>83</v>
+      </c>
+      <c r="D34" t="s">
+        <v>44</v>
+      </c>
+      <c r="E34" t="s">
+        <v>29</v>
+      </c>
+      <c r="F34">
+        <v>163</v>
+      </c>
+      <c r="G34" t="s">
+        <v>30</v>
+      </c>
+      <c r="H34">
+        <v>2849</v>
+      </c>
+      <c r="I34">
+        <v>1.445068</v>
+      </c>
+      <c r="J34">
+        <v>17.171779140000002</v>
+      </c>
+      <c r="K34" t="s">
+        <v>37</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>2799</v>
+      </c>
+      <c r="N34" t="s">
+        <v>52</v>
+      </c>
+      <c r="O34">
+        <v>4117</v>
+      </c>
+      <c r="P34">
+        <v>679.86397899999997</v>
+      </c>
+      <c r="Q34">
+        <v>163</v>
+      </c>
+      <c r="S34">
+        <v>17.171779000000001</v>
+      </c>
+      <c r="T34">
+        <v>3.9591940000000001</v>
+      </c>
+      <c r="U34">
+        <v>179</v>
+      </c>
+      <c r="V34">
+        <v>4.3478260000000004</v>
+      </c>
+      <c r="W34">
+        <v>15.636872</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>25</v>
+      </c>
+      <c r="B35" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D35" t="s">
+        <v>44</v>
+      </c>
+      <c r="E35" t="s">
+        <v>29</v>
+      </c>
+      <c r="F35">
+        <v>6</v>
+      </c>
+      <c r="G35" t="s">
+        <v>30</v>
+      </c>
+      <c r="H35">
+        <v>121</v>
+      </c>
+      <c r="I35">
+        <v>1.016529</v>
+      </c>
+      <c r="J35">
+        <v>14.33333333</v>
+      </c>
+      <c r="K35">
+        <v>160</v>
+      </c>
+      <c r="L35" t="s">
+        <v>31</v>
+      </c>
+      <c r="M35">
+        <v>86</v>
+      </c>
+      <c r="N35" t="s">
+        <v>40</v>
+      </c>
+      <c r="O35">
+        <v>123</v>
+      </c>
+      <c r="P35">
+        <v>699.18699200000003</v>
+      </c>
+      <c r="Q35">
+        <v>6</v>
+      </c>
+      <c r="S35">
+        <v>14.333333</v>
+      </c>
+      <c r="T35">
+        <v>4.8780489999999999</v>
+      </c>
+      <c r="U35">
+        <v>6</v>
+      </c>
+      <c r="V35">
+        <v>4.8780489999999999</v>
+      </c>
+      <c r="W35">
+        <v>14.333333</v>
       </c>
     </row>
   </sheetData>
